--- a/src/test/resources/writer/verticalFor/vertical_for_cell_set_jsonnodes.xlsx
+++ b/src/test/resources/writer/verticalFor/vertical_for_cell_set_jsonnodes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/h_yamazaki/git/actier/forma4j/src/test/resources/writer/verticalFor/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/h_yamazaki/repo/actier/forma4j/src/test/resources/writer/verticalFor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8425B7A-91B5-064F-A915-0A614C086633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9774B099-EA7D-B446-8FCE-4F8B2DC54DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="test" sheetId="1" r:id="rId1"/>
@@ -459,33 +459,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
